--- a/docs/downloads/09/t8_transition_alaotra_tous.xlsx
+++ b/docs/downloads/09/t8_transition_alaotra_tous.xlsx
@@ -489,12 +489,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3.2</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -558,12 +552,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>4.6</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,12 +569,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -604,12 +586,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -627,12 +603,6 @@
           <t>Autres mélanges</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -696,12 +666,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <v>5.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -719,12 +683,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16">
-        <v>5.2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -788,12 +746,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -857,12 +809,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22">
-        <v>9.5</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -880,12 +826,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>4.8</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -903,12 +843,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -972,12 +906,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D27">
-        <v>2</v>
-      </c>
-      <c r="E27">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -995,12 +923,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1018,12 +940,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1041,12 +957,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1064,12 +974,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1087,12 +991,6 @@
           <t>Autres mélanges</t>
         </is>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1110,12 +1008,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1133,12 +1025,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1156,12 +1042,6 @@
           <t>Riz</t>
         </is>
       </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1179,12 +1059,6 @@
           <t>Tubercule+Céréale</t>
         </is>
       </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1271,12 +1145,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1294,12 +1162,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D41">
-        <v>2</v>
-      </c>
-      <c r="E41">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1317,12 +1179,6 @@
           <t>Maïs</t>
         </is>
       </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1340,12 +1196,6 @@
           <t>Riz</t>
         </is>
       </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1363,12 +1213,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1386,12 +1230,6 @@
           <t>Autres mélanges</t>
         </is>
       </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1478,12 +1316,6 @@
           <t>Autres mélanges</t>
         </is>
       </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>4.2</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1501,12 +1333,6 @@
           <t>Patate douce</t>
         </is>
       </c>
-      <c r="D50">
-        <v>2</v>
-      </c>
-      <c r="E50">
-        <v>2.8</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1524,12 +1350,6 @@
           <t>Manioc</t>
         </is>
       </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>1.4</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1546,12 +1366,6 @@
         <is>
           <t>Maïs</t>
         </is>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>1.4</v>
       </c>
     </row>
     <row r="53">

--- a/docs/downloads/09/t8_transition_alaotra_tous.xlsx
+++ b/docs/downloads/09/t8_transition_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -516,7 +516,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -556,7 +556,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1086,7 +1086,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1166,7 +1166,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1200,7 +1200,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1234,7 +1234,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1394,7 +1394,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
